--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/TEXAS_2015.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/TEXAS_2015.xlsx
@@ -499,7 +499,7 @@
         <v>222</v>
       </c>
       <c r="D8">
-        <v>0.0009940357852882703</v>
+        <v>0.0009940357852882705</v>
       </c>
     </row>
     <row r="9">
@@ -2785,7 +2785,7 @@
         <v>22</v>
       </c>
       <c r="D135">
-        <v>9.850805079433309E-05</v>
+        <v>9.850805079433308E-05</v>
       </c>
     </row>
     <row r="136">
@@ -3919,7 +3919,7 @@
         <v>223</v>
       </c>
       <c r="D198">
-        <v>0.0009985134239607401</v>
+        <v>0.0009985134239607399</v>
       </c>
     </row>
     <row r="199">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C202">
@@ -4963,7 +4963,7 @@
         <v>207</v>
       </c>
       <c r="D256">
-        <v>0.0009268712052012251</v>
+        <v>0.0009268712052012252</v>
       </c>
     </row>
     <row r="257">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C267">
@@ -5215,7 +5215,7 @@
         <v>22</v>
       </c>
       <c r="D270">
-        <v>9.850805079433309E-05</v>
+        <v>9.850805079433308E-05</v>
       </c>
     </row>
     <row r="271">
@@ -5575,7 +5575,7 @@
         <v>22</v>
       </c>
       <c r="D290">
-        <v>9.850805079433309E-05</v>
+        <v>9.850805079433308E-05</v>
       </c>
     </row>
     <row r="291">
@@ -7735,7 +7735,7 @@
         <v>22</v>
       </c>
       <c r="D410">
-        <v>9.850805079433309E-05</v>
+        <v>9.850805079433308E-05</v>
       </c>
     </row>
     <row r="411">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C425">
@@ -8599,7 +8599,7 @@
         <v>223</v>
       </c>
       <c r="D458">
-        <v>0.0009985134239607401</v>
+        <v>0.0009985134239607399</v>
       </c>
     </row>
     <row r="459">
@@ -9283,7 +9283,7 @@
         <v>22</v>
       </c>
       <c r="D496">
-        <v>9.850805079433309E-05</v>
+        <v>9.850805079433308E-05</v>
       </c>
     </row>
     <row r="497">
@@ -9517,7 +9517,7 @@
         <v>205</v>
       </c>
       <c r="D509">
-        <v>0.0009179159278562857</v>
+        <v>0.0009179159278562856</v>
       </c>
     </row>
     <row r="510">
@@ -12325,7 +12325,7 @@
         <v>22</v>
       </c>
       <c r="D665">
-        <v>9.850805079433309E-05</v>
+        <v>9.850805079433308E-05</v>
       </c>
     </row>
     <row r="666">
@@ -13279,7 +13279,7 @@
         <v>22</v>
       </c>
       <c r="D718">
-        <v>9.850805079433309E-05</v>
+        <v>9.850805079433308E-05</v>
       </c>
     </row>
     <row r="719">
@@ -15727,7 +15727,7 @@
         <v>22</v>
       </c>
       <c r="D854">
-        <v>9.850805079433309E-05</v>
+        <v>9.850805079433308E-05</v>
       </c>
     </row>
     <row r="855">
@@ -16609,7 +16609,7 @@
         <v>22</v>
       </c>
       <c r="D903">
-        <v>9.850805079433309E-05</v>
+        <v>9.850805079433308E-05</v>
       </c>
     </row>
     <row r="904">
@@ -16951,7 +16951,7 @@
         <v>205</v>
       </c>
       <c r="D922">
-        <v>0.0009179159278562857</v>
+        <v>0.0009179159278562856</v>
       </c>
     </row>
     <row r="923">
@@ -16980,7 +16980,7 @@
       </c>
       <c r="B924" t="inlineStr">
         <is>
-          <t>General Escobedo</t>
+          <t>Gral. Escobedo</t>
         </is>
       </c>
       <c r="C924">
@@ -17016,7 +17016,7 @@
       </c>
       <c r="B926" t="inlineStr">
         <is>
-          <t>General Trevino</t>
+          <t>Gral. Trevino</t>
         </is>
       </c>
       <c r="C926">
@@ -17034,7 +17034,7 @@
       </c>
       <c r="B927" t="inlineStr">
         <is>
-          <t>General Zaragoza</t>
+          <t>Gral. Zaragoza</t>
         </is>
       </c>
       <c r="C927">
@@ -20346,7 +20346,7 @@
       </c>
       <c r="B1111" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C1111">
@@ -20364,7 +20364,7 @@
       </c>
       <c r="B1112" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C1112">
@@ -21696,7 +21696,7 @@
       </c>
       <c r="B1186" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C1186">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="B1187" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C1187">
@@ -26257,7 +26257,7 @@
         <v>22</v>
       </c>
       <c r="D1439">
-        <v>9.850805079433309E-05</v>
+        <v>9.850805079433308E-05</v>
       </c>
     </row>
     <row r="1440">
@@ -26527,7 +26527,7 @@
         <v>22</v>
       </c>
       <c r="D1454">
-        <v>9.850805079433309E-05</v>
+        <v>9.850805079433308E-05</v>
       </c>
     </row>
     <row r="1455">
@@ -28489,7 +28489,7 @@
         <v>22</v>
       </c>
       <c r="D1563">
-        <v>9.850805079433309E-05</v>
+        <v>9.850805079433308E-05</v>
       </c>
     </row>
     <row r="1564">
@@ -28759,7 +28759,7 @@
         <v>212</v>
       </c>
       <c r="D1578">
-        <v>0.0009492593985635735</v>
+        <v>0.0009492593985635736</v>
       </c>
     </row>
     <row r="1579">
@@ -29497,7 +29497,7 @@
         <v>22</v>
       </c>
       <c r="D1619">
-        <v>9.850805079433309E-05</v>
+        <v>9.850805079433308E-05</v>
       </c>
     </row>
     <row r="1620">
@@ -32496,7 +32496,7 @@
       </c>
       <c r="B1786" t="inlineStr">
         <is>
-          <t>Ziltlaltepec De Trinidad Sanchez Santos</t>
+          <t>Zitlaltepec De Trinidad Sanchez Santos</t>
         </is>
       </c>
       <c r="C1786">
@@ -34015,7 +34015,7 @@
         <v>22</v>
       </c>
       <c r="D1870">
-        <v>9.850805079433309E-05</v>
+        <v>9.850805079433308E-05</v>
       </c>
     </row>
     <row r="1871">
@@ -34825,7 +34825,7 @@
         <v>22</v>
       </c>
       <c r="D1915">
-        <v>9.850805079433309E-05</v>
+        <v>9.850805079433308E-05</v>
       </c>
     </row>
     <row r="1916">
@@ -35977,7 +35977,7 @@
         <v>212</v>
       </c>
       <c r="D1979">
-        <v>0.0009492593985635735</v>
+        <v>0.0009492593985635736</v>
       </c>
     </row>
     <row r="1980">
@@ -36103,7 +36103,7 @@
         <v>22</v>
       </c>
       <c r="D1986">
-        <v>9.850805079433309E-05</v>
+        <v>9.850805079433308E-05</v>
       </c>
     </row>
     <row r="1987">
@@ -36985,7 +36985,7 @@
         <v>207</v>
       </c>
       <c r="D2035">
-        <v>0.0009268712052012251</v>
+        <v>0.0009268712052012252</v>
       </c>
     </row>
     <row r="2036">
@@ -37453,7 +37453,7 @@
         <v>22</v>
       </c>
       <c r="D2061">
-        <v>9.850805079433309E-05</v>
+        <v>9.850805079433308E-05</v>
       </c>
     </row>
     <row r="2062">
